--- a/conversion_file.xlsx
+++ b/conversion_file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeff.tenbosch/Library/CloudStorage/GoogleDrive-jeff.tenbosch@databricks.com/My Drive/Downloads (Google)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeff.tenbosch/Library/CloudStorage/GoogleDrive-jeff.tenbosch@databricks.com/My Drive/code/cursor/data_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7BEBA1-76B0-EB47-BE4E-79A6233B66FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A155A5BC-D26A-2F47-928B-003CFB178F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13660" yWindow="4380" windowWidth="49160" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>billing_transactions_hhd</t>
-  </si>
-  <si>
-    <t>invc_nbr,mat_nbr, cal_month</t>
   </si>
   <si>
     <t>WITH cte1 AS ( SELECT [BILL_NUM], [BILL_ITEM], FISCVARNT, CALMONTH, COUNT(*) AS duplicate_count FROM raw_abdc_operations.sapbw_billingtransactionlvl1 WHERE zzrefinv != '' AND bill_type IN ('zrk1', 'zrk2') AND ZPRICEOWN IN ('10', '20', '30', '40') AND salesorg IN ('1000', '2000', '1200') AND CAST(CREATED AS DATE) BETWEEN DATEADD(day, -180, GETDATE()) AND GETDATE() GROUP BY [BILL_NUM], [BILL_ITEM], FISCVARNT, CALMONTH ) SELECT 'BILL_NUM || BILL_ITEM || FISCVARNT || CALMONTH' AS PRIMARY_KEY_NAME, CAST(BILL_NUM AS VARCHAR) + ' || ' + CAST(BILL_ITEM AS VARCHAR) + ' || ' + CAST(FISCVARNT AS VARCHAR) + ' || ' + CAST(CALMONTH AS VARCHAR) AS PRIMARY_KEY_VALUE, 'BILL_NUM || BILL_ITEM || FISCVARNT || CALMONTH' AS ATTRIBUTE_NAME, CAST(BILL_NUM AS VARCHAR) + ' || ' + CAST(BILL_ITEM AS VARCHAR) + ' || ' + CAST(FISCVARNT AS VARCHAR) + ' || ' + CAST(CALMONTH AS VARCHAR) AS ATTRIBUTE_VALUE, 'duplicate_count' AS ADDITIONAL_COLUMN_NAME, duplicate_count AS ADDITIONAL_COLUMN_VALUE FROM cte1</t>
@@ -1786,12 +1783,15 @@
   <si>
     <t>SOURCE_SQL_STATEMENT</t>
   </si>
+  <si>
+    <t>invc_nbr,mat_nbr,fiscal_variant, cal_month</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1802,12 +1802,21 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1838,19 +1847,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2081,25 +2091,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2141,65 +2151,65 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -2211,18 +2221,18 @@
         <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="238" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -2231,159 +2241,159 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2</v>
@@ -2395,18 +2405,18 @@
         <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -2415,205 +2425,205 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2</v>
@@ -2625,18 +2635,18 @@
         <v>10</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
@@ -2648,18 +2658,18 @@
         <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
@@ -2671,110 +2681,110 @@
         <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>2</v>
@@ -2786,41 +2796,41 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="187" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -2832,18 +2842,18 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -2852,67 +2862,67 @@
         <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -2924,18 +2934,18 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
@@ -2947,18 +2957,18 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -2970,18 +2980,18 @@
         <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
@@ -2993,64 +3003,64 @@
         <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>2</v>
@@ -3062,18 +3072,18 @@
         <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>2</v>
@@ -3085,133 +3095,133 @@
         <v>10</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
@@ -3223,18 +3233,18 @@
         <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>2</v>
@@ -3246,18 +3256,18 @@
         <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>2</v>
@@ -3269,18 +3279,18 @@
         <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
@@ -3292,18 +3302,18 @@
         <v>10</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>2</v>
@@ -3315,18 +3325,18 @@
         <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
@@ -3338,18 +3348,18 @@
         <v>10</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
@@ -3361,18 +3371,18 @@
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
@@ -3384,18 +3394,18 @@
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
@@ -3407,18 +3417,18 @@
         <v>10</v>
       </c>
       <c r="F58" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
@@ -3430,87 +3440,87 @@
         <v>10</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="G62" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>2</v>
@@ -3522,18 +3532,18 @@
         <v>10</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>2</v>
@@ -3545,18 +3555,18 @@
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>2</v>
@@ -3568,110 +3578,110 @@
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" s="1" t="s">
+      <c r="G67" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>2</v>
@@ -3683,18 +3693,18 @@
         <v>10</v>
       </c>
       <c r="F70" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>2</v>
@@ -3706,110 +3716,110 @@
         <v>10</v>
       </c>
       <c r="F71" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="372" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="F75" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>2</v>
@@ -3821,87 +3831,87 @@
         <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="G78" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>2</v>
@@ -3913,18 +3923,18 @@
         <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>2</v>
@@ -3936,570 +3946,570 @@
         <v>10</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="G83" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="G87" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="G88" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F89" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="G90" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="136" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="G91" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="G92" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="G94" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F97" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G97" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="F98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="G98" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F99" s="1" t="s">
+      <c r="G99" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C100" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="306" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="F101" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="G101" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="G103" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="238" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="G104" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="306" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E105" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="G105" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>2</v>
@@ -4508,21 +4518,21 @@
         <v>9</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
@@ -4531,21 +4541,21 @@
         <v>9</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
@@ -4554,21 +4564,21 @@
         <v>9</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
@@ -4577,228 +4587,228 @@
         <v>9</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="G110" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="F111" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="G111" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="F112" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="G112" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="1" t="s">
+      <c r="G113" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F114" s="1" t="s">
+      <c r="G114" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F115" s="1" t="s">
+      <c r="G115" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F116" s="1" t="s">
+      <c r="G116" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F117" s="1" t="s">
+      <c r="G117" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F118" s="1" t="s">
+      <c r="G118" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
@@ -4810,202 +4820,202 @@
         <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G119" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D120" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="F121" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="G121" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D122" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="F122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="G122" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G123" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G124" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G125" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G126" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>2</v>
@@ -5014,274 +5024,274 @@
         <v>9</v>
       </c>
       <c r="E128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="G128" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F129" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G129" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G130" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G131" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D132" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="F132" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="238" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C134" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F135" s="1" t="s">
+      <c r="G135" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F137" s="1" t="s">
+      <c r="G137" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F138" s="1" t="s">
+      <c r="G138" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="F139" s="1" t="s">
+      <c r="G139" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>2</v>
@@ -5290,21 +5300,21 @@
         <v>9</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>2</v>
@@ -5313,67 +5323,67 @@
         <v>9</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G142" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="G143" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>2</v>
@@ -5382,289 +5392,289 @@
         <v>9</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="F145" s="1" t="s">
+      <c r="G145" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G146" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G147" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G148" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C149" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="F149" s="1" t="s">
+      <c r="G149" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F151" s="1" t="s">
+      <c r="G151" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="F152" s="1" t="s">
+      <c r="G152" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F154" s="1" t="s">
+      <c r="G154" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F155" s="1" t="s">
+      <c r="G155" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="170" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F156" s="1" t="s">
+      <c r="G156" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
